--- a/data/trans_dic/P25A$otro-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,77</t>
+          <t>0,99; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,43</t>
+          <t>0,69; 4,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 15,01</t>
+          <t>6,53; 14,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,03</t>
+          <t>1,44; 11,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 31,18</t>
+          <t>4,54; 28,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,57</t>
+          <t>1,09; 4,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,71</t>
+          <t>1,14; 4,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 14,9</t>
+          <t>6,85; 14,98</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,29</t>
+          <t>0,44; 3,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,29</t>
+          <t>1,12; 4,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,24</t>
+          <t>6,02; 12,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 21,98</t>
+          <t>10,18; 22,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,72</t>
+          <t>3,3; 9,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 18,21</t>
+          <t>8,61; 18,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,13</t>
+          <t>4,84; 10,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,57</t>
+          <t>2,42; 5,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 13,4</t>
+          <t>7,86; 13,4</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,54</t>
+          <t>0,98; 9,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 17,9</t>
+          <t>5,48; 18,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 19,08</t>
+          <t>1,93; 18,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 22,26</t>
+          <t>7,69; 23,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,74</t>
+          <t>2,05; 10,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,68</t>
+          <t>0,56; 5,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 18,32</t>
+          <t>7,48; 18,01</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,85</t>
+          <t>1,29; 3,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,57</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,3</t>
+          <t>7,35; 11,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,29</t>
+          <t>7,57; 15,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,42</t>
+          <t>3,17; 7,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,26</t>
+          <t>9,37; 17,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,47</t>
+          <t>3,45; 6,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,28</t>
+          <t>2,11; 4,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,78</t>
+          <t>8,85; 12,93</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2930; 14466</t>
+          <t>2990; 14972</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2957; 16491</t>
+          <t>2561; 15463</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13477; 31500</t>
+          <t>13708; 31167</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>986; 8308</t>
+          <t>997; 8199</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1141; 11734</t>
+          <t>1707; 10772</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3790; 16049</t>
+          <t>3842; 16519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5113; 20792</t>
+          <t>5018; 19160</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16814; 36873</t>
+          <t>16956; 37073</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1038; 10159</t>
+          <t>1042; 9460</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3842; 14923</t>
+          <t>3899; 15297</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17778; 36979</t>
+          <t>18177; 38528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15056; 33244</t>
+          <t>15400; 34251</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7834; 23346</t>
+          <t>7923; 23371</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17234; 36611</t>
+          <t>17314; 36640</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18609; 39329</t>
+          <t>18779; 38836</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13425; 32720</t>
+          <t>14216; 32786</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40233; 67408</t>
+          <t>39548; 67430</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>819; 8056</t>
+          <t>823; 7791</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6696</t>
+          <t>0; 6494</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4086; 16037</t>
+          <t>4907; 16715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>990; 9801</t>
+          <t>990; 9354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6289</t>
+          <t>0; 6113</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6847; 21162</t>
+          <t>7307; 22252</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2548; 13226</t>
+          <t>2782; 14124</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>976; 9867</t>
+          <t>972; 9842</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14768; 33832</t>
+          <t>13820; 33253</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8406; 24022</t>
+          <t>8086; 24256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10634; 29115</t>
+          <t>9690; 27799</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45105; 74005</t>
+          <t>44180; 71387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18170; 38337</t>
+          <t>18981; 39836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11097; 28684</t>
+          <t>12242; 29632</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33337; 57623</t>
+          <t>31290; 57955</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30420; 56623</t>
+          <t>30197; 55524</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25667; 51431</t>
+          <t>25339; 49613</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82011; 119549</t>
+          <t>82783; 120963</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$otro-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Estudios-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,94</t>
+          <t>1,06; 4,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,16</t>
+          <t>0,8; 4,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,85</t>
+          <t>6,62; 14,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,87</t>
+          <t>1,44; 12,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 28,63</t>
+          <t>3,01; 30,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,7</t>
+          <t>1,09; 4,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,34</t>
+          <t>1,18; 4,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,98</t>
+          <t>6,72; 14,68</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,99</t>
+          <t>0,45; 4,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,4</t>
+          <t>0,94; 4,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,76</t>
+          <t>5,92; 12,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 22,65</t>
+          <t>10,22; 22,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,73</t>
+          <t>3,0; 9,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,22</t>
+          <t>8,41; 18,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,0</t>
+          <t>4,89; 10,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,58</t>
+          <t>2,48; 5,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,4</t>
+          <t>7,59; 13,25</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,23</t>
+          <t>0,98; 8,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 6,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 18,65</t>
+          <t>5,21; 19,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,21</t>
+          <t>1,88; 16,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 9,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 23,41</t>
+          <t>7,82; 22,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 10,4</t>
+          <t>1,76; 10,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,67</t>
+          <t>0,56; 5,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 18,01</t>
+          <t>7,67; 18,15</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,88</t>
+          <t>1,31; 3,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,41</t>
+          <t>1,1; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 11,87</t>
+          <t>7,29; 12,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,89</t>
+          <t>7,47; 15,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,67</t>
+          <t>2,91; 7,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,36</t>
+          <t>9,64; 17,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,34</t>
+          <t>3,52; 6,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,13</t>
+          <t>2,07; 4,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,93</t>
+          <t>8,85; 12,95</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2990; 14972</t>
+          <t>3219; 14660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2561; 15463</t>
+          <t>2989; 15551</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13708; 31167</t>
+          <t>13892; 30191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>0; 3370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>997; 8199</t>
+          <t>995; 8301</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1707; 10772</t>
+          <t>1134; 11385</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3842; 16519</t>
+          <t>3842; 16157</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5018; 19160</t>
+          <t>5209; 20818</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16956; 37073</t>
+          <t>16640; 36336</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1042; 9460</t>
+          <t>1059; 10821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3899; 15297</t>
+          <t>3257; 14472</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18177; 38528</t>
+          <t>17880; 37861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15400; 34251</t>
+          <t>15447; 33685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7923; 23371</t>
+          <t>7210; 22334</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17314; 36640</t>
+          <t>16915; 37183</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18779; 38836</t>
+          <t>19002; 39510</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14216; 32786</t>
+          <t>14593; 32407</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39548; 67430</t>
+          <t>38191; 66652</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>823; 7791</t>
+          <t>826; 7132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6494</t>
+          <t>0; 6564</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4907; 16715</t>
+          <t>4666; 17361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>990; 9354</t>
+          <t>968; 8263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6113</t>
+          <t>0; 7379</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7307; 22252</t>
+          <t>7437; 21762</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2782; 14124</t>
+          <t>2389; 13954</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>972; 9842</t>
+          <t>976; 9360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13820; 33253</t>
+          <t>14162; 33514</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8086; 24256</t>
+          <t>8171; 23471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9690; 27799</t>
+          <t>8965; 27330</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44180; 71387</t>
+          <t>43836; 72511</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18981; 39836</t>
+          <t>18728; 38528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12242; 29632</t>
+          <t>11235; 29119</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31290; 57955</t>
+          <t>32182; 57030</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30197; 55524</t>
+          <t>30810; 55759</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25339; 49613</t>
+          <t>24869; 48291</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82783; 120963</t>
+          <t>82725; 121090</t>
         </is>
       </c>
     </row>
